--- a/docs/steel_ratio/鉄筋比問題集.xlsx
+++ b/docs/steel_ratio/鉄筋比問題集.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目次" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上限下限値早見表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-1 柱pg・梁pt" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-2 柱梁pw" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-3 壁ps" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-4 釣合鉄筋比" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-5 適切な鉄筋量" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="解答" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="目次" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="上限下限値早見表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="5-1 柱pg・梁pt" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="5-2 柱梁pw" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5-3 壁ps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5-4 釣合鉄筋比" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="5-5 適切な鉄筋量" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="解答" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -220,7 +220,37 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3600450"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -235,13 +265,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -249,8 +282,8 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -265,13 +298,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -279,8 +315,8 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -295,13 +331,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -309,8 +348,8 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -325,13 +364,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -339,8 +381,8 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -355,13 +397,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -858,7 +903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1079,13 +1124,22 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>■ 補足図（理解の整理）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1532,8 +1586,8 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A56:H56"/>
     <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A56:H56"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A53:H53"/>
